--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/core2s/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EEF25476-B12E-45D4-A545-B6A7F31C32AC}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6A14642-71D4-43AF-B637-B77EDED742B9}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="457" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="308">
   <si>
     <t>Total Cost</t>
   </si>
@@ -954,6 +954,12 @@
   </si>
   <si>
     <t>MDR-40-48 100-240VAC</t>
+  </si>
+  <si>
+    <t>Flange, 304/304L Stainless Steel, Metal Pipe Flange - 60WJ74|4381000040 - Grainger</t>
+  </si>
+  <si>
+    <t>Flange  Blind ("plug")</t>
   </si>
 </sst>
 </file>
@@ -1370,6 +1376,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K120" totalsRowShown="0" tableBorderDxfId="7">
   <autoFilter ref="A1:K120" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
@@ -4615,7 +4625,9 @@
       <c r="H119" s="10"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="29"/>
+      <c r="A120" s="29" t="s">
+        <v>307</v>
+      </c>
       <c r="B120" s="23"/>
       <c r="C120" s="10"/>
       <c r="D120" s="30"/>
@@ -4624,7 +4636,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="H120" s="10"/>
+      <c r="H120" s="1" t="s">
+        <v>306</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4739,11 +4753,12 @@
     <hyperlink ref="H116" r:id="rId108" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C0D4D21-381D-4DE0-8627-C5CDD08AC966}"/>
     <hyperlink ref="H117" r:id="rId109" display="https://www.grainger.com/product/Compression-Lug-3-8-in-Stud-24C366" xr:uid="{969E4A0C-E52F-4A17-A6F5-A3D01F24676B}"/>
     <hyperlink ref="H118" r:id="rId110" display="https://www.digikey.com/en/products/detail/advantech-corporation/bb-mdr-40-48/7426468" xr:uid="{65E538F7-DA33-4388-B23E-404C55813446}"/>
+    <hyperlink ref="H120" r:id="rId111" display="https://www.grainger.com/product/Metal-Pipe-Flange-Flange-60WJ74" xr:uid="{851EBC08-2ED2-4124-B23F-E667A9F9321B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId111"/>
+  <pageSetup orientation="portrait" r:id="rId112"/>
   <tableParts count="1">
-    <tablePart r:id="rId112"/>
+    <tablePart r:id="rId113"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/core2s/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6A14642-71D4-43AF-B637-B77EDED742B9}"/>
+  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37B114D0-B60A-46D7-8DDB-4A7D5D693ACF}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="459" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="314">
   <si>
     <t>Total Cost</t>
   </si>
@@ -960,6 +960,24 @@
   </si>
   <si>
     <t>Flange  Blind ("plug")</t>
+  </si>
+  <si>
+    <t>Metal Pipe Flange: Flange, 304/304L Stainless Steel, 1 1/2 in Pipe Size, Class 150, Raised, 285 psi</t>
+  </si>
+  <si>
+    <t>500A Current Sensor</t>
+  </si>
+  <si>
+    <t>N1HLR-2700MV/KA-5V PULSE Egston | Current Sensors | DigiKey</t>
+  </si>
+  <si>
+    <t>CURRENT SENS ROGOWSKI INTEGR 5V</t>
+  </si>
+  <si>
+    <t>6385-N1HLR-2700MV/KA-5V-ND</t>
+  </si>
+  <si>
+    <t>60WJ74</t>
   </si>
 </sst>
 </file>
@@ -1134,7 +1152,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1263,6 +1281,28 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1381,8 +1421,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K120" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K120" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K128" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K128" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1719,7 +1759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M120"/>
+  <dimension ref="A1:M128"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
@@ -4481,7 +4521,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4505,7 +4545,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4529,7 +4569,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A115" s="13"/>
       <c r="B115" s="23"/>
       <c r="C115" s="10"/>
@@ -4541,7 +4581,7 @@
       </c>
       <c r="H115" s="10"/>
     </row>
-    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="39" t="s">
         <v>302</v>
       </c>
@@ -4566,7 +4606,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>298</v>
       </c>
@@ -4590,7 +4630,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
         <v>304</v>
       </c>
@@ -4612,7 +4652,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A119" s="13"/>
       <c r="B119" s="23"/>
       <c r="C119" s="10"/>
@@ -4624,21 +4664,173 @@
       </c>
       <c r="H119" s="10"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="29" t="s">
+    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A120" s="46" t="s">
         <v>307</v>
       </c>
-      <c r="B120" s="23"/>
-      <c r="C120" s="10"/>
-      <c r="D120" s="30"/>
-      <c r="E120" s="30"/>
-      <c r="F120" s="6">
+      <c r="B120" s="48" t="s">
+        <v>308</v>
+      </c>
+      <c r="C120" s="49" t="s">
+        <v>313</v>
+      </c>
+      <c r="D120" s="8">
+        <v>2</v>
+      </c>
+      <c r="E120" s="8">
+        <v>85.47</v>
+      </c>
+      <c r="F120" s="50">
         <f t="shared" si="5"/>
+        <v>170.94</v>
+      </c>
+      <c r="G120" s="51"/>
+      <c r="H120" s="53" t="s">
+        <v>306</v>
+      </c>
+      <c r="I120" s="51"/>
+      <c r="J120" s="51"/>
+      <c r="K120" s="51"/>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A121" s="46" t="s">
+        <v>309</v>
+      </c>
+      <c r="B121" s="48" t="s">
+        <v>311</v>
+      </c>
+      <c r="C121" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="D121" s="8">
+        <v>1</v>
+      </c>
+      <c r="E121" s="8">
+        <v>90.93</v>
+      </c>
+      <c r="F121" s="50">
+        <f t="shared" ref="F121:F128" si="6">D121*E121</f>
+        <v>90.93</v>
+      </c>
+      <c r="G121" s="51"/>
+      <c r="H121" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="I121" s="51"/>
+      <c r="J121" s="51"/>
+      <c r="K121" s="51"/>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A122" s="46"/>
+      <c r="B122" s="48"/>
+      <c r="C122" s="49"/>
+      <c r="D122" s="8"/>
+      <c r="E122" s="8"/>
+      <c r="F122" s="50">
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="H120" s="1" t="s">
-        <v>306</v>
-      </c>
+      <c r="G122" s="51"/>
+      <c r="H122" s="52"/>
+      <c r="I122" s="51"/>
+      <c r="J122" s="51"/>
+      <c r="K122" s="51"/>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A123" s="46"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="49"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="50">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G123" s="51"/>
+      <c r="H123" s="52"/>
+      <c r="I123" s="51"/>
+      <c r="J123" s="51"/>
+      <c r="K123" s="51"/>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A124" s="46"/>
+      <c r="B124" s="48"/>
+      <c r="C124" s="49"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8"/>
+      <c r="F124" s="50">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G124" s="51"/>
+      <c r="H124" s="52"/>
+      <c r="I124" s="51"/>
+      <c r="J124" s="51"/>
+      <c r="K124" s="51"/>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A125" s="46"/>
+      <c r="B125" s="48"/>
+      <c r="C125" s="49"/>
+      <c r="D125" s="8"/>
+      <c r="E125" s="8"/>
+      <c r="F125" s="50">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G125" s="51"/>
+      <c r="H125" s="52"/>
+      <c r="I125" s="51"/>
+      <c r="J125" s="51"/>
+      <c r="K125" s="51"/>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A126" s="46"/>
+      <c r="B126" s="48"/>
+      <c r="C126" s="49"/>
+      <c r="D126" s="8"/>
+      <c r="E126" s="8"/>
+      <c r="F126" s="50">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G126" s="51"/>
+      <c r="H126" s="52"/>
+      <c r="I126" s="51"/>
+      <c r="J126" s="51"/>
+      <c r="K126" s="51"/>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A127" s="46"/>
+      <c r="B127" s="48"/>
+      <c r="C127" s="49"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="50">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G127" s="51"/>
+      <c r="H127" s="52"/>
+      <c r="I127" s="51"/>
+      <c r="J127" s="51"/>
+      <c r="K127" s="51"/>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A128" s="47"/>
+      <c r="B128" s="48"/>
+      <c r="C128" s="49"/>
+      <c r="D128" s="30"/>
+      <c r="E128" s="30"/>
+      <c r="F128" s="50">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="G128" s="51"/>
+      <c r="H128" s="52"/>
+      <c r="I128" s="51"/>
+      <c r="J128" s="51"/>
+      <c r="K128" s="51"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4754,11 +4946,12 @@
     <hyperlink ref="H117" r:id="rId109" display="https://www.grainger.com/product/Compression-Lug-3-8-in-Stud-24C366" xr:uid="{969E4A0C-E52F-4A17-A6F5-A3D01F24676B}"/>
     <hyperlink ref="H118" r:id="rId110" display="https://www.digikey.com/en/products/detail/advantech-corporation/bb-mdr-40-48/7426468" xr:uid="{65E538F7-DA33-4388-B23E-404C55813446}"/>
     <hyperlink ref="H120" r:id="rId111" display="https://www.grainger.com/product/Metal-Pipe-Flange-Flange-60WJ74" xr:uid="{851EBC08-2ED2-4124-B23F-E667A9F9321B}"/>
+    <hyperlink ref="H121" r:id="rId112" display="https://www.digikey.com/en/products/detail/pulse-egston/N1HLR-2700MV-KA-5V/29410171?gclid=d0e0296f6f231fb67a4543cf4f2a21d9&amp;gclsrc=3p.ds&amp;msclkid=d0e0296f6f231fb67a4543cf4f2a21d9" xr:uid="{54E9C926-24F1-4758-853F-BD129F6EBDFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId112"/>
+  <pageSetup orientation="portrait" r:id="rId113"/>
   <tableParts count="1">
-    <tablePart r:id="rId113"/>
+    <tablePart r:id="rId114"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/core2s/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="23" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{37B114D0-B60A-46D7-8DDB-4A7D5D693ACF}"/>
+  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7097742-8680-4A14-B6FB-49CE99DCED95}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="465" uniqueCount="314">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="322">
   <si>
     <t>Total Cost</t>
   </si>
@@ -978,6 +978,30 @@
   </si>
   <si>
     <t>60WJ74</t>
+  </si>
+  <si>
+    <t>TIB100A - Functional Devices TIB100A - Transformer 96VA, 120 to 24 Vac, Circuit Breaker, DIN Rail Mount</t>
+  </si>
+  <si>
+    <t>Transformer 96VA, 120 to 24 Vac, Circuit Breaker, DIN Rail Mount</t>
+  </si>
+  <si>
+    <t>TIB100A</t>
+  </si>
+  <si>
+    <t>24V AC PSU, From Supply House</t>
+  </si>
+  <si>
+    <t>24V AC PSU, From Digikey</t>
+  </si>
+  <si>
+    <t>TIB100A Functional Devices | Industrial, DIN Rail Power Supplies | DigiKey Marketplace</t>
+  </si>
+  <si>
+    <t>120-24VAC 96VA CIRCUIT BREAKER</t>
+  </si>
+  <si>
+    <t>2272-TIB100A-ND</t>
   </si>
 </sst>
 </file>
@@ -1152,7 +1176,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1281,26 +1305,16 @@
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -4521,7 +4535,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4545,7 +4559,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4569,7 +4583,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="13"/>
       <c r="B115" s="23"/>
       <c r="C115" s="10"/>
@@ -4581,7 +4595,7 @@
       </c>
       <c r="H115" s="10"/>
     </row>
-    <row r="116" spans="1:11" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A116" s="39" t="s">
         <v>302</v>
       </c>
@@ -4606,7 +4620,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="117" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
         <v>298</v>
       </c>
@@ -4630,7 +4644,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="13" t="s">
         <v>304</v>
       </c>
@@ -4652,7 +4666,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="13"/>
       <c r="B119" s="23"/>
       <c r="C119" s="10"/>
@@ -4664,14 +4678,14 @@
       </c>
       <c r="H119" s="10"/>
     </row>
-    <row r="120" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A120" s="46" t="s">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A120" s="13" t="s">
         <v>307</v>
       </c>
-      <c r="B120" s="48" t="s">
+      <c r="B120" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="C120" s="49" t="s">
+      <c r="C120" s="10" t="s">
         <v>313</v>
       </c>
       <c r="D120" s="8">
@@ -4680,26 +4694,22 @@
       <c r="E120" s="8">
         <v>85.47</v>
       </c>
-      <c r="F120" s="50">
+      <c r="F120" s="6">
         <f t="shared" si="5"/>
         <v>170.94</v>
       </c>
-      <c r="G120" s="51"/>
-      <c r="H120" s="53" t="s">
+      <c r="H120" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="I120" s="51"/>
-      <c r="J120" s="51"/>
-      <c r="K120" s="51"/>
-    </row>
-    <row r="121" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A121" s="46" t="s">
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A121" s="13" t="s">
         <v>309</v>
       </c>
-      <c r="B121" s="48" t="s">
+      <c r="B121" s="23" t="s">
         <v>311</v>
       </c>
-      <c r="C121" s="49" t="s">
+      <c r="C121" s="10" t="s">
         <v>312</v>
       </c>
       <c r="D121" s="8">
@@ -4708,129 +4718,121 @@
       <c r="E121" s="8">
         <v>90.93</v>
       </c>
-      <c r="F121" s="50">
+      <c r="F121" s="6">
         <f t="shared" ref="F121:F128" si="6">D121*E121</f>
         <v>90.93</v>
       </c>
-      <c r="G121" s="51"/>
       <c r="H121" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="I121" s="51"/>
-      <c r="J121" s="51"/>
-      <c r="K121" s="51"/>
-    </row>
-    <row r="122" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A122" s="46"/>
-      <c r="B122" s="48"/>
-      <c r="C122" s="49"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A122" s="13"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="10"/>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
-      <c r="F122" s="50">
+      <c r="F122" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G122" s="51"/>
-      <c r="H122" s="52"/>
-      <c r="I122" s="51"/>
-      <c r="J122" s="51"/>
-      <c r="K122" s="51"/>
-    </row>
-    <row r="123" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A123" s="46"/>
-      <c r="B123" s="48"/>
-      <c r="C123" s="49"/>
-      <c r="D123" s="8"/>
-      <c r="E123" s="8"/>
-      <c r="F123" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G123" s="51"/>
-      <c r="H123" s="52"/>
-      <c r="I123" s="51"/>
-      <c r="J123" s="51"/>
-      <c r="K123" s="51"/>
-    </row>
-    <row r="124" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A124" s="46"/>
-      <c r="B124" s="48"/>
-      <c r="C124" s="49"/>
-      <c r="D124" s="8"/>
-      <c r="E124" s="8"/>
-      <c r="F124" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G124" s="51"/>
-      <c r="H124" s="52"/>
-      <c r="I124" s="51"/>
-      <c r="J124" s="51"/>
-      <c r="K124" s="51"/>
-    </row>
-    <row r="125" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A125" s="46"/>
+      <c r="H122" s="10"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A123" s="13" t="s">
+        <v>318</v>
+      </c>
+      <c r="B123" s="23" t="s">
+        <v>320</v>
+      </c>
+      <c r="C123" s="10" t="s">
+        <v>321</v>
+      </c>
+      <c r="D123" s="8">
+        <v>1</v>
+      </c>
+      <c r="E123" s="8">
+        <v>93.8</v>
+      </c>
+      <c r="F123" s="6">
+        <f>D123*E123</f>
+        <v>93.8</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A124" s="13" t="s">
+        <v>317</v>
+      </c>
+      <c r="B124" s="23" t="s">
+        <v>315</v>
+      </c>
+      <c r="C124" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="D124" s="8">
+        <v>1</v>
+      </c>
+      <c r="E124" s="8">
+        <v>70.349999999999994</v>
+      </c>
+      <c r="F124" s="6">
+        <f>D124*E124</f>
+        <v>70.349999999999994</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A125" s="47"/>
       <c r="B125" s="48"/>
       <c r="C125" s="49"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
-      <c r="F125" s="50">
+      <c r="F125" s="6">
+        <f>D125*E125</f>
+        <v>0</v>
+      </c>
+      <c r="H125" s="10"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A126" s="13"/>
+      <c r="B126" s="23"/>
+      <c r="C126" s="10"/>
+      <c r="D126" s="8"/>
+      <c r="E126" s="8"/>
+      <c r="F126" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G125" s="51"/>
-      <c r="H125" s="52"/>
-      <c r="I125" s="51"/>
-      <c r="J125" s="51"/>
-      <c r="K125" s="51"/>
-    </row>
-    <row r="126" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A126" s="46"/>
-      <c r="B126" s="48"/>
-      <c r="C126" s="49"/>
-      <c r="D126" s="8"/>
-      <c r="E126" s="8"/>
-      <c r="F126" s="50">
+      <c r="H126" s="10"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A127" s="13"/>
+      <c r="B127" s="23"/>
+      <c r="C127" s="10"/>
+      <c r="D127" s="8"/>
+      <c r="E127" s="8"/>
+      <c r="F127" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G126" s="51"/>
-      <c r="H126" s="52"/>
-      <c r="I126" s="51"/>
-      <c r="J126" s="51"/>
-      <c r="K126" s="51"/>
-    </row>
-    <row r="127" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A127" s="46"/>
-      <c r="B127" s="48"/>
-      <c r="C127" s="49"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
-      <c r="F127" s="50">
+      <c r="H127" s="10"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A128" s="29"/>
+      <c r="B128" s="23"/>
+      <c r="C128" s="10"/>
+      <c r="D128" s="30"/>
+      <c r="E128" s="30"/>
+      <c r="F128" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="G127" s="51"/>
-      <c r="H127" s="52"/>
-      <c r="I127" s="51"/>
-      <c r="J127" s="51"/>
-      <c r="K127" s="51"/>
-    </row>
-    <row r="128" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A128" s="47"/>
-      <c r="B128" s="48"/>
-      <c r="C128" s="49"/>
-      <c r="D128" s="30"/>
-      <c r="E128" s="30"/>
-      <c r="F128" s="50">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="G128" s="51"/>
-      <c r="H128" s="52"/>
-      <c r="I128" s="51"/>
-      <c r="J128" s="51"/>
-      <c r="K128" s="51"/>
+      <c r="H128" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4947,11 +4949,13 @@
     <hyperlink ref="H118" r:id="rId110" display="https://www.digikey.com/en/products/detail/advantech-corporation/bb-mdr-40-48/7426468" xr:uid="{65E538F7-DA33-4388-B23E-404C55813446}"/>
     <hyperlink ref="H120" r:id="rId111" display="https://www.grainger.com/product/Metal-Pipe-Flange-Flange-60WJ74" xr:uid="{851EBC08-2ED2-4124-B23F-E667A9F9321B}"/>
     <hyperlink ref="H121" r:id="rId112" display="https://www.digikey.com/en/products/detail/pulse-egston/N1HLR-2700MV-KA-5V/29410171?gclid=d0e0296f6f231fb67a4543cf4f2a21d9&amp;gclsrc=3p.ds&amp;msclkid=d0e0296f6f231fb67a4543cf4f2a21d9" xr:uid="{54E9C926-24F1-4758-853F-BD129F6EBDFF}"/>
+    <hyperlink ref="H124" r:id="rId113" display="https://www.supplyhouse.com/Functional-Devices-TIB100A-Transformer-96VA-120-to-24-Vac-Circuit-Breaker-DIN-Rail-Mount?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{0A2C36B1-5125-4F51-8575-F092A696C03C}"/>
+    <hyperlink ref="H123" r:id="rId114" display="https://www.digikey.com/en/products/detail/aim-dynamics/TIB100A/28736836?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{74179639-4519-4C59-BD73-C785247C9073}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId113"/>
+  <pageSetup orientation="portrait" r:id="rId115"/>
   <tableParts count="1">
-    <tablePart r:id="rId114"/>
+    <tablePart r:id="rId116"/>
   </tableParts>
 </worksheet>
 </file>
--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/core2s/resources/v0.1.2/design_documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\thermal-loop\resources\v0.1.2\design_documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="50" documentId="13_ncr:1_{55AB40B0-6C17-4ECF-ABEA-EBBE2E37FDFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7097742-8680-4A14-B6FB-49CE99DCED95}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823F2AAE-25ED-44E6-8A76-EF5843E5E1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="322">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="319">
   <si>
     <t>Total Cost</t>
   </si>
@@ -983,18 +983,6 @@
     <t>TIB100A - Functional Devices TIB100A - Transformer 96VA, 120 to 24 Vac, Circuit Breaker, DIN Rail Mount</t>
   </si>
   <si>
-    <t>Transformer 96VA, 120 to 24 Vac, Circuit Breaker, DIN Rail Mount</t>
-  </si>
-  <si>
-    <t>TIB100A</t>
-  </si>
-  <si>
-    <t>24V AC PSU, From Supply House</t>
-  </si>
-  <si>
-    <t>24V AC PSU, From Digikey</t>
-  </si>
-  <si>
     <t>TIB100A Functional Devices | Industrial, DIN Rail Power Supplies | DigiKey Marketplace</t>
   </si>
   <si>
@@ -1002,6 +990,9 @@
   </si>
   <si>
     <t>2272-TIB100A-ND</t>
+  </si>
+  <si>
+    <t>24V AC PSU</t>
   </si>
 </sst>
 </file>
@@ -1176,7 +1167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1308,15 +1299,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1430,13 +1412,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K128" totalsRowShown="0" tableBorderDxfId="7">
-  <autoFilter ref="A1:K128" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}" name="Table1" displayName="Table1" ref="A1:K127" totalsRowShown="0" tableBorderDxfId="7">
+  <autoFilter ref="A1:K127" xr:uid="{3AC99790-742C-414B-AF83-048E0365A8B5}"/>
   <tableColumns count="11">
     <tableColumn id="1" xr3:uid="{7B25C464-EB0A-4B56-94DE-96F6AA8DEAC1}" name="Internal Part Name" dataDxfId="6"/>
     <tableColumn id="2" xr3:uid="{DF8C1AF7-50DF-4DF9-864F-041981FCACF8}" name="MFR / Vendor Description" dataDxfId="5"/>
@@ -1773,25 +1751,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
-  <dimension ref="A1:M128"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M127"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" customWidth="1"/>
-    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.44140625" customWidth="1"/>
+    <col min="2" max="2" width="33.140625" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.42578125" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.44140625" customWidth="1"/>
-    <col min="11" max="11" width="62.44140625" customWidth="1"/>
-    <col min="12" max="12" width="55.6640625" customWidth="1"/>
+    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.42578125" customWidth="1"/>
+    <col min="11" max="11" width="62.42578125" customWidth="1"/>
+    <col min="12" max="12" width="55.7109375" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1826,7 +1804,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -1852,7 +1830,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -1878,7 +1856,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
@@ -1903,7 +1881,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
@@ -1929,7 +1907,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
@@ -1955,7 +1933,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
@@ -1983,7 +1961,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
@@ -2009,7 +1987,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -2036,7 +2014,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -2061,7 +2039,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
@@ -2087,7 +2065,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
@@ -2111,7 +2089,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
         <v>19</v>
       </c>
@@ -2137,7 +2115,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
@@ -2163,7 +2141,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
@@ -2189,7 +2167,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>22</v>
       </c>
@@ -2215,7 +2193,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
@@ -2241,7 +2219,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
@@ -2265,7 +2243,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
@@ -2291,7 +2269,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2317,7 +2295,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
@@ -2343,7 +2321,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
         <v>28</v>
       </c>
@@ -2369,7 +2347,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
@@ -2395,7 +2373,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
         <v>30</v>
       </c>
@@ -2421,7 +2399,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
@@ -2447,7 +2425,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
@@ -2473,7 +2451,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
@@ -2498,7 +2476,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="s">
         <v>32</v>
       </c>
@@ -2522,7 +2500,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
@@ -2546,7 +2524,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
@@ -2570,7 +2548,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
@@ -2594,7 +2572,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
@@ -2618,7 +2596,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
@@ -2642,7 +2620,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
         <v>36</v>
       </c>
@@ -2666,7 +2644,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="13" t="s">
         <v>37</v>
       </c>
@@ -2690,7 +2668,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="12" t="s">
         <v>37</v>
       </c>
@@ -2714,7 +2692,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
@@ -2738,7 +2716,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
@@ -2762,7 +2740,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
@@ -2786,7 +2764,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="12" t="s">
         <v>12</v>
       </c>
@@ -2810,7 +2788,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
         <v>39</v>
       </c>
@@ -2834,7 +2812,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
@@ -2858,7 +2836,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="13" t="s">
         <v>41</v>
       </c>
@@ -2882,7 +2860,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
@@ -2906,7 +2884,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="13" t="s">
         <v>43</v>
       </c>
@@ -2930,7 +2908,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
@@ -2954,7 +2932,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="13" t="s">
         <v>45</v>
       </c>
@@ -2978,7 +2956,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
@@ -3002,7 +2980,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="13" t="s">
         <v>46</v>
       </c>
@@ -3026,7 +3004,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" s="12" t="s">
         <v>47</v>
       </c>
@@ -3050,7 +3028,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="13" t="s">
         <v>46</v>
       </c>
@@ -3074,7 +3052,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -3098,7 +3076,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="13" t="s">
         <v>48</v>
       </c>
@@ -3122,7 +3100,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -3146,7 +3124,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
@@ -3170,7 +3148,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="12" t="s">
         <v>35</v>
       </c>
@@ -3194,7 +3172,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="13" t="s">
         <v>48</v>
       </c>
@@ -3218,7 +3196,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="12" t="s">
         <v>39</v>
       </c>
@@ -3242,7 +3220,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="13" t="s">
         <v>12</v>
       </c>
@@ -3266,7 +3244,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="12" t="s">
         <v>51</v>
       </c>
@@ -3290,7 +3268,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
@@ -3314,7 +3292,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="12" t="s">
         <v>52</v>
       </c>
@@ -3338,7 +3316,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="13" t="s">
         <v>52</v>
       </c>
@@ -3362,7 +3340,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
         <v>48</v>
       </c>
@@ -3386,7 +3364,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="13" t="s">
         <v>45</v>
       </c>
@@ -3410,7 +3388,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
@@ -3434,7 +3412,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="13" t="s">
         <v>53</v>
       </c>
@@ -3458,7 +3436,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="12" t="s">
         <v>45</v>
       </c>
@@ -3482,7 +3460,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="13" t="s">
         <v>54</v>
       </c>
@@ -3506,7 +3484,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="12" t="s">
         <v>54</v>
       </c>
@@ -3530,7 +3508,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="13" t="s">
         <v>55</v>
       </c>
@@ -3554,7 +3532,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="12" t="s">
         <v>46</v>
       </c>
@@ -3578,7 +3556,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="13" t="s">
         <v>56</v>
       </c>
@@ -3602,7 +3580,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="12" t="s">
         <v>57</v>
       </c>
@@ -3626,7 +3604,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="13" t="s">
         <v>11</v>
       </c>
@@ -3650,7 +3628,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="12" t="s">
         <v>58</v>
       </c>
@@ -3674,7 +3652,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="13" t="s">
         <v>46</v>
       </c>
@@ -3698,7 +3676,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="12" t="s">
         <v>39</v>
       </c>
@@ -3722,7 +3700,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="13" t="s">
         <v>59</v>
       </c>
@@ -3746,7 +3724,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="12" t="s">
         <v>60</v>
       </c>
@@ -3770,7 +3748,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="13" t="s">
         <v>61</v>
       </c>
@@ -3794,7 +3772,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="12" t="s">
         <v>62</v>
       </c>
@@ -3818,7 +3796,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="13" t="s">
         <v>63</v>
       </c>
@@ -3842,7 +3820,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="12" t="s">
         <v>64</v>
       </c>
@@ -3866,7 +3844,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
@@ -3890,7 +3868,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="12" t="s">
         <v>63</v>
       </c>
@@ -3914,7 +3892,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="13" t="s">
         <v>65</v>
       </c>
@@ -3938,7 +3916,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="12" t="s">
         <v>63</v>
       </c>
@@ -3962,7 +3940,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="13" t="s">
         <v>66</v>
       </c>
@@ -3986,7 +3964,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
@@ -4010,7 +3988,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="13" t="s">
         <v>46</v>
       </c>
@@ -4034,7 +4012,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
@@ -4056,7 +4034,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
@@ -4080,7 +4058,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
@@ -4104,7 +4082,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
@@ -4128,7 +4106,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="13" t="s">
         <v>68</v>
       </c>
@@ -4150,7 +4128,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A97" s="13" t="s">
         <v>69</v>
       </c>
@@ -4172,7 +4150,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A98" s="13" t="s">
         <v>67</v>
       </c>
@@ -4196,7 +4174,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A99" s="13" t="s">
         <v>70</v>
       </c>
@@ -4220,7 +4198,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A100" s="13" t="s">
         <v>66</v>
       </c>
@@ -4244,7 +4222,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A101" s="13" t="s">
         <v>17</v>
       </c>
@@ -4268,7 +4246,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A102" s="13" t="s">
         <v>61</v>
       </c>
@@ -4292,7 +4270,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A103" s="13" t="s">
         <v>71</v>
       </c>
@@ -4316,7 +4294,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A104" s="29" t="s">
         <v>258</v>
       </c>
@@ -4340,7 +4318,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A105" s="29" t="s">
         <v>259</v>
       </c>
@@ -4364,7 +4342,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A106" s="29" t="s">
         <v>260</v>
       </c>
@@ -4387,7 +4365,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A107" s="13" t="s">
         <v>294</v>
       </c>
@@ -4411,7 +4389,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A108" s="13" t="s">
         <v>293</v>
       </c>
@@ -4435,7 +4413,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A109" s="13" t="s">
         <v>292</v>
       </c>
@@ -4459,7 +4437,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="33" t="s">
         <v>291</v>
       </c>
@@ -4483,7 +4461,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="39" t="s">
         <v>17</v>
       </c>
@@ -4511,7 +4489,7 @@
       <c r="J111" s="23"/>
       <c r="K111" s="23"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A112" s="13" t="s">
         <v>61</v>
       </c>
@@ -4535,7 +4513,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4559,7 +4537,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4583,7 +4561,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A115" s="13"/>
       <c r="B115" s="23"/>
       <c r="C115" s="10"/>
@@ -4595,7 +4573,7 @@
       </c>
       <c r="H115" s="10"/>
     </row>
-    <row r="116" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="39" t="s">
         <v>302</v>
       </c>
@@ -4620,7 +4598,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A117" s="13" t="s">
         <v>298</v>
       </c>
@@ -4644,7 +4622,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A118" s="13" t="s">
         <v>304</v>
       </c>
@@ -4666,7 +4644,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A119" s="13"/>
       <c r="B119" s="23"/>
       <c r="C119" s="10"/>
@@ -4678,7 +4656,7 @@
       </c>
       <c r="H119" s="10"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A120" s="13" t="s">
         <v>307</v>
       </c>
@@ -4702,7 +4680,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A121" s="13" t="s">
         <v>309</v>
       </c>
@@ -4719,14 +4697,14 @@
         <v>90.93</v>
       </c>
       <c r="F121" s="6">
-        <f t="shared" ref="F121:F128" si="6">D121*E121</f>
+        <f t="shared" ref="F121:F127" si="6">D121*E121</f>
         <v>90.93</v>
       </c>
       <c r="H121" s="1" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A122" s="13"/>
       <c r="B122" s="23"/>
       <c r="C122" s="10"/>
@@ -4738,15 +4716,15 @@
       </c>
       <c r="H122" s="10"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A123" s="13" t="s">
         <v>318</v>
       </c>
       <c r="B123" s="23" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="C123" s="10" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="D123" s="8">
         <v>1</v>
@@ -4759,46 +4737,37 @@
         <v>93.8</v>
       </c>
       <c r="H123" s="1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="13" t="s">
-        <v>317</v>
-      </c>
-      <c r="B124" s="23" t="s">
         <v>315</v>
       </c>
-      <c r="C124" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="D124" s="8">
-        <v>1</v>
-      </c>
-      <c r="E124" s="8">
-        <v>70.349999999999994</v>
-      </c>
+      <c r="I123" s="1" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A124" s="13"/>
+      <c r="B124" s="23"/>
+      <c r="C124" s="10"/>
+      <c r="D124" s="8"/>
+      <c r="E124" s="8"/>
       <c r="F124" s="6">
         <f>D124*E124</f>
-        <v>70.349999999999994</v>
-      </c>
-      <c r="H124" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="47"/>
-      <c r="B125" s="48"/>
-      <c r="C125" s="49"/>
+        <v>0</v>
+      </c>
+      <c r="H124" s="10"/>
+    </row>
+    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A125" s="13"/>
+      <c r="B125" s="23"/>
+      <c r="C125" s="10"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
       <c r="F125" s="6">
-        <f>D125*E125</f>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H125" s="10"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A126" s="13"/>
       <c r="B126" s="23"/>
       <c r="C126" s="10"/>
@@ -4810,29 +4779,17 @@
       </c>
       <c r="H126" s="10"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="13"/>
+    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A127" s="29"/>
       <c r="B127" s="23"/>
       <c r="C127" s="10"/>
-      <c r="D127" s="8"/>
-      <c r="E127" s="8"/>
+      <c r="D127" s="30"/>
+      <c r="E127" s="30"/>
       <c r="F127" s="6">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="H127" s="10"/>
-    </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="29"/>
-      <c r="B128" s="23"/>
-      <c r="C128" s="10"/>
-      <c r="D128" s="30"/>
-      <c r="E128" s="30"/>
-      <c r="F128" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="H128" s="10"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -4949,7 +4906,7 @@
     <hyperlink ref="H118" r:id="rId110" display="https://www.digikey.com/en/products/detail/advantech-corporation/bb-mdr-40-48/7426468" xr:uid="{65E538F7-DA33-4388-B23E-404C55813446}"/>
     <hyperlink ref="H120" r:id="rId111" display="https://www.grainger.com/product/Metal-Pipe-Flange-Flange-60WJ74" xr:uid="{851EBC08-2ED2-4124-B23F-E667A9F9321B}"/>
     <hyperlink ref="H121" r:id="rId112" display="https://www.digikey.com/en/products/detail/pulse-egston/N1HLR-2700MV-KA-5V/29410171?gclid=d0e0296f6f231fb67a4543cf4f2a21d9&amp;gclsrc=3p.ds&amp;msclkid=d0e0296f6f231fb67a4543cf4f2a21d9" xr:uid="{54E9C926-24F1-4758-853F-BD129F6EBDFF}"/>
-    <hyperlink ref="H124" r:id="rId113" display="https://www.supplyhouse.com/Functional-Devices-TIB100A-Transformer-96VA-120-to-24-Vac-Circuit-Breaker-DIN-Rail-Mount?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{0A2C36B1-5125-4F51-8575-F092A696C03C}"/>
+    <hyperlink ref="I123" r:id="rId113" display="https://www.supplyhouse.com/Functional-Devices-TIB100A-Transformer-96VA-120-to-24-Vac-Circuit-Breaker-DIN-Rail-Mount?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{0A2C36B1-5125-4F51-8575-F092A696C03C}"/>
     <hyperlink ref="H123" r:id="rId114" display="https://www.digikey.com/en/products/detail/aim-dynamics/TIB100A/28736836?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{74179639-4519-4C59-BD73-C785247C9073}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
+++ b/resources/v0.1.2/design_documents/BOM-V0.1.2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\adowney2\Documents\GitHub\thermal-loop\resources\v0.1.2\design_documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/c1ed1b07ceb518fe/Documents/GitHub/core2s/resources/v0.1.2/design_documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{823F2AAE-25ED-44E6-8A76-EF5843E5E1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{823F2AAE-25ED-44E6-8A76-EF5843E5E1BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{06DD01CF-4235-41BE-AB0D-DE5285124C05}"/>
   <bookViews>
-    <workbookView xWindow="-16320" yWindow="-6540" windowWidth="16440" windowHeight="28320" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{FDAE7DA4-9528-4FC7-A320-70DA50473DCE}"/>
   </bookViews>
   <sheets>
     <sheet name="bill_of_materials" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="470" uniqueCount="319">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="315">
   <si>
     <t>Total Cost</t>
   </si>
@@ -930,18 +930,6 @@
   </si>
   <si>
     <t>20XM55</t>
-  </si>
-  <si>
-    <t>Lug Terminal</t>
-  </si>
-  <si>
-    <t>Compression Lug: 3/8 in Stud Size, 4/0 AWG – 4/0 AWG For Wire Sizes, Stranded Wire Type, Std, Copper</t>
-  </si>
-  <si>
-    <t>24C366</t>
-  </si>
-  <si>
-    <t>3/8 in Stud Size, 4/0 AWG – 4/0 AWG For Wire Sizes, Compression Lug - 24C366|24C366 - Grainger</t>
   </si>
   <si>
     <t>NiChrome Rod joining Compression Fitting</t>
@@ -1167,7 +1155,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1297,6 +1285,15 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -1752,24 +1749,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C6D3A36C-E8CE-4E50-A172-E48E2F9A45A8}">
   <dimension ref="A1:M127"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39" customWidth="1"/>
-    <col min="2" max="2" width="33.140625" customWidth="1"/>
-    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.42578125" customWidth="1"/>
+    <col min="2" max="2" width="33.109375" customWidth="1"/>
+    <col min="3" max="3" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.44140625" customWidth="1"/>
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="79" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="83.42578125" customWidth="1"/>
-    <col min="11" max="11" width="62.42578125" customWidth="1"/>
-    <col min="12" max="12" width="55.7109375" customWidth="1"/>
+    <col min="9" max="9" width="45.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="83.44140625" customWidth="1"/>
+    <col min="11" max="11" width="62.44140625" customWidth="1"/>
+    <col min="12" max="12" width="55.6640625" customWidth="1"/>
     <col min="13" max="13" width="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
@@ -1804,7 +1801,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="12" t="s">
         <v>10</v>
       </c>
@@ -1830,7 +1827,7 @@
       </c>
       <c r="J2" s="2"/>
     </row>
-    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="13" t="s">
         <v>11</v>
       </c>
@@ -1856,7 +1853,7 @@
       </c>
       <c r="I3" s="4"/>
     </row>
-    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
         <v>12</v>
       </c>
@@ -1881,7 +1878,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="13" t="s">
         <v>10</v>
       </c>
@@ -1907,7 +1904,7 @@
       </c>
       <c r="I5" s="1"/>
     </row>
-    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="12" t="s">
         <v>10</v>
       </c>
@@ -1933,7 +1930,7 @@
       </c>
       <c r="I6" s="4"/>
     </row>
-    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
@@ -1961,7 +1958,7 @@
       <c r="J7" s="3"/>
       <c r="K7" s="3"/>
     </row>
-    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="12" t="s">
         <v>14</v>
       </c>
@@ -1987,7 +1984,7 @@
       </c>
       <c r="I8" s="4"/>
     </row>
-    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="13" t="s">
         <v>15</v>
       </c>
@@ -2014,7 +2011,7 @@
       <c r="L9" s="4"/>
       <c r="M9" s="4"/>
     </row>
-    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="12" t="s">
         <v>16</v>
       </c>
@@ -2039,7 +2036,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="13" t="s">
         <v>17</v>
       </c>
@@ -2065,7 +2062,7 @@
       </c>
       <c r="I11" s="3"/>
     </row>
-    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="12" t="s">
         <v>18</v>
       </c>
@@ -2089,7 +2086,7 @@
       </c>
       <c r="I12" s="4"/>
     </row>
-    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="13" t="s">
         <v>19</v>
       </c>
@@ -2115,7 +2112,7 @@
       </c>
       <c r="I13" s="4"/>
     </row>
-    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>20</v>
       </c>
@@ -2141,7 +2138,7 @@
       </c>
       <c r="I14" s="4"/>
     </row>
-    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="13" t="s">
         <v>21</v>
       </c>
@@ -2167,7 +2164,7 @@
       </c>
       <c r="I15" s="4"/>
     </row>
-    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>22</v>
       </c>
@@ -2193,7 +2190,7 @@
       </c>
       <c r="I16" s="4"/>
     </row>
-    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="13" t="s">
         <v>23</v>
       </c>
@@ -2219,7 +2216,7 @@
       </c>
       <c r="I17" s="4"/>
     </row>
-    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="12" t="s">
         <v>24</v>
       </c>
@@ -2243,7 +2240,7 @@
       </c>
       <c r="I18" s="4"/>
     </row>
-    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="13" t="s">
         <v>25</v>
       </c>
@@ -2269,7 +2266,7 @@
       </c>
       <c r="I19" s="4"/>
     </row>
-    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>26</v>
       </c>
@@ -2295,7 +2292,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="13" t="s">
         <v>27</v>
       </c>
@@ -2321,7 +2318,7 @@
       </c>
       <c r="I21" s="4"/>
     </row>
-    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="12" t="s">
         <v>28</v>
       </c>
@@ -2347,7 +2344,7 @@
       </c>
       <c r="I22" s="4"/>
     </row>
-    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="13" t="s">
         <v>29</v>
       </c>
@@ -2373,7 +2370,7 @@
       </c>
       <c r="I23" s="4"/>
     </row>
-    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="12" t="s">
         <v>30</v>
       </c>
@@ -2399,7 +2396,7 @@
       </c>
       <c r="I24" s="4"/>
     </row>
-    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="13" t="s">
         <v>28</v>
       </c>
@@ -2425,7 +2422,7 @@
       </c>
       <c r="I25" s="4"/>
     </row>
-    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="12" t="s">
         <v>31</v>
       </c>
@@ -2451,7 +2448,7 @@
       </c>
       <c r="I26" s="2"/>
     </row>
-    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="13" t="s">
         <v>17</v>
       </c>
@@ -2476,7 +2473,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="12" t="s">
         <v>32</v>
       </c>
@@ -2500,7 +2497,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="13" t="s">
         <v>33</v>
       </c>
@@ -2524,7 +2521,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="12" t="s">
         <v>34</v>
       </c>
@@ -2548,7 +2545,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="13" t="s">
         <v>35</v>
       </c>
@@ -2572,7 +2569,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="12" t="s">
         <v>35</v>
       </c>
@@ -2596,7 +2593,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="13" t="s">
         <v>36</v>
       </c>
@@ -2620,7 +2617,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="12" t="s">
         <v>36</v>
       </c>
@@ -2644,7 +2641,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="13" t="s">
         <v>37</v>
       </c>
@@ -2668,7 +2665,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="12" t="s">
         <v>37</v>
       </c>
@@ -2692,7 +2689,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="13" t="s">
         <v>35</v>
       </c>
@@ -2716,7 +2713,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="12" t="s">
         <v>38</v>
       </c>
@@ -2740,7 +2737,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="13" t="s">
         <v>38</v>
       </c>
@@ -2764,7 +2761,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="12" t="s">
         <v>12</v>
       </c>
@@ -2788,7 +2785,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="13" t="s">
         <v>39</v>
       </c>
@@ -2812,7 +2809,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="12" t="s">
         <v>40</v>
       </c>
@@ -2836,7 +2833,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="13" t="s">
         <v>41</v>
       </c>
@@ -2860,7 +2857,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="12" t="s">
         <v>42</v>
       </c>
@@ -2884,7 +2881,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="13" t="s">
         <v>43</v>
       </c>
@@ -2908,7 +2905,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="12" t="s">
         <v>44</v>
       </c>
@@ -2932,7 +2929,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="13" t="s">
         <v>45</v>
       </c>
@@ -2956,7 +2953,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="12" t="s">
         <v>45</v>
       </c>
@@ -2980,7 +2977,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="13" t="s">
         <v>46</v>
       </c>
@@ -3004,7 +3001,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="12" t="s">
         <v>47</v>
       </c>
@@ -3028,7 +3025,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="13" t="s">
         <v>46</v>
       </c>
@@ -3052,7 +3049,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="12" t="s">
         <v>46</v>
       </c>
@@ -3076,7 +3073,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="13" t="s">
         <v>48</v>
       </c>
@@ -3100,7 +3097,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="12" t="s">
         <v>49</v>
       </c>
@@ -3124,7 +3121,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
@@ -3148,7 +3145,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="12" t="s">
         <v>35</v>
       </c>
@@ -3172,7 +3169,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="13" t="s">
         <v>48</v>
       </c>
@@ -3196,7 +3193,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="12" t="s">
         <v>39</v>
       </c>
@@ -3220,7 +3217,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="13" t="s">
         <v>12</v>
       </c>
@@ -3244,7 +3241,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="12" t="s">
         <v>51</v>
       </c>
@@ -3268,7 +3265,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="13" t="s">
         <v>46</v>
       </c>
@@ -3292,7 +3289,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="12" t="s">
         <v>52</v>
       </c>
@@ -3316,7 +3313,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="13" t="s">
         <v>52</v>
       </c>
@@ -3340,7 +3337,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="12" t="s">
         <v>48</v>
       </c>
@@ -3364,7 +3361,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="13" t="s">
         <v>45</v>
       </c>
@@ -3388,7 +3385,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="12" t="s">
         <v>37</v>
       </c>
@@ -3412,7 +3409,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="13" t="s">
         <v>53</v>
       </c>
@@ -3436,7 +3433,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="12" t="s">
         <v>45</v>
       </c>
@@ -3460,7 +3457,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="13" t="s">
         <v>54</v>
       </c>
@@ -3484,7 +3481,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="12" t="s">
         <v>54</v>
       </c>
@@ -3508,7 +3505,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="13" t="s">
         <v>55</v>
       </c>
@@ -3532,7 +3529,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="12" t="s">
         <v>46</v>
       </c>
@@ -3556,7 +3553,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="13" t="s">
         <v>56</v>
       </c>
@@ -3580,7 +3577,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="12" t="s">
         <v>57</v>
       </c>
@@ -3604,7 +3601,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="13" t="s">
         <v>11</v>
       </c>
@@ -3628,7 +3625,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="12" t="s">
         <v>58</v>
       </c>
@@ -3652,7 +3649,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="13" t="s">
         <v>46</v>
       </c>
@@ -3676,7 +3673,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="12" t="s">
         <v>39</v>
       </c>
@@ -3700,7 +3697,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="13" t="s">
         <v>59</v>
       </c>
@@ -3724,7 +3721,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="12" t="s">
         <v>60</v>
       </c>
@@ -3748,7 +3745,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="13" t="s">
         <v>61</v>
       </c>
@@ -3772,7 +3769,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="12" t="s">
         <v>62</v>
       </c>
@@ -3796,7 +3793,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="13" t="s">
         <v>63</v>
       </c>
@@ -3820,7 +3817,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="12" t="s">
         <v>64</v>
       </c>
@@ -3844,7 +3841,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="13" t="s">
         <v>35</v>
       </c>
@@ -3868,7 +3865,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="12" t="s">
         <v>63</v>
       </c>
@@ -3892,7 +3889,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="13" t="s">
         <v>65</v>
       </c>
@@ -3916,7 +3913,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>63</v>
       </c>
@@ -3940,7 +3937,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="13" t="s">
         <v>66</v>
       </c>
@@ -3964,7 +3961,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="13" t="s">
         <v>67</v>
       </c>
@@ -3988,7 +3985,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="13" t="s">
         <v>46</v>
       </c>
@@ -4012,7 +4009,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="13" t="s">
         <v>68</v>
       </c>
@@ -4034,7 +4031,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>264</v>
       </c>
@@ -4058,7 +4055,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="13" t="s">
         <v>268</v>
       </c>
@@ -4082,7 +4079,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="13" t="s">
         <v>269</v>
       </c>
@@ -4106,7 +4103,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="13" t="s">
         <v>68</v>
       </c>
@@ -4128,7 +4125,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A97" s="13" t="s">
         <v>69</v>
       </c>
@@ -4150,7 +4147,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="13" t="s">
         <v>67</v>
       </c>
@@ -4174,7 +4171,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A99" s="13" t="s">
         <v>70</v>
       </c>
@@ -4198,7 +4195,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A100" s="13" t="s">
         <v>66</v>
       </c>
@@ -4222,7 +4219,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="13" t="s">
         <v>17</v>
       </c>
@@ -4246,7 +4243,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A102" s="13" t="s">
         <v>61</v>
       </c>
@@ -4270,7 +4267,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A103" s="13" t="s">
         <v>71</v>
       </c>
@@ -4294,7 +4291,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="29" t="s">
         <v>258</v>
       </c>
@@ -4318,7 +4315,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A105" s="29" t="s">
         <v>259</v>
       </c>
@@ -4342,7 +4339,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A106" s="29" t="s">
         <v>260</v>
       </c>
@@ -4365,7 +4362,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="13" t="s">
         <v>294</v>
       </c>
@@ -4389,7 +4386,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A108" s="13" t="s">
         <v>293</v>
       </c>
@@ -4413,7 +4410,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A109" s="13" t="s">
         <v>292</v>
       </c>
@@ -4437,7 +4434,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:11" s="24" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A110" s="33" t="s">
         <v>291</v>
       </c>
@@ -4461,7 +4458,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:11" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A111" s="39" t="s">
         <v>17</v>
       </c>
@@ -4489,7 +4486,7 @@
       <c r="J111" s="23"/>
       <c r="K111" s="23"/>
     </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A112" s="13" t="s">
         <v>61</v>
       </c>
@@ -4513,7 +4510,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="13" t="s">
         <v>17</v>
       </c>
@@ -4537,7 +4534,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="13" t="s">
         <v>66</v>
       </c>
@@ -4561,110 +4558,106 @@
         <v>243</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A115" s="13"/>
-      <c r="B115" s="23"/>
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A115" s="13" t="s">
+        <v>300</v>
+      </c>
+      <c r="B115" s="45" t="s">
+        <v>301</v>
+      </c>
       <c r="C115" s="10"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
+      <c r="D115" s="8">
+        <v>1</v>
+      </c>
+      <c r="E115" s="8">
+        <v>14.79</v>
+      </c>
       <c r="F115" s="6">
-        <f t="shared" ref="F115:F120" si="5">D115*E115</f>
-        <v>0</v>
-      </c>
-      <c r="H115" s="10"/>
-    </row>
-    <row r="116" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="39" t="s">
-        <v>302</v>
-      </c>
-      <c r="B116" s="40" t="s">
-        <v>288</v>
-      </c>
-      <c r="C116" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="D116" s="42">
-        <v>1</v>
-      </c>
-      <c r="E116" s="42">
-        <v>14.99</v>
-      </c>
-      <c r="F116" s="43">
-        <f t="shared" si="5"/>
-        <v>14.99</v>
-      </c>
-      <c r="G116" s="23"/>
-      <c r="H116" s="44" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.25">
+        <f>D115*E115</f>
+        <v>14.79</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="13" t="s">
+        <v>314</v>
+      </c>
+      <c r="B116" s="23" t="s">
+        <v>312</v>
+      </c>
+      <c r="C116" s="10" t="s">
+        <v>313</v>
+      </c>
+      <c r="D116" s="8">
+        <v>1</v>
+      </c>
+      <c r="E116" s="8">
+        <v>93.8</v>
+      </c>
+      <c r="F116" s="6">
+        <f>D116*E116</f>
+        <v>93.8</v>
+      </c>
+      <c r="H116" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="I116" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="13" t="s">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="B117" s="23" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C117" s="10" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="D117" s="8">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E117" s="8">
-        <v>6.37</v>
+        <v>90.93</v>
       </c>
       <c r="F117" s="6">
-        <f t="shared" si="5"/>
-        <v>19.11</v>
+        <f>D117*E117</f>
+        <v>90.93</v>
       </c>
       <c r="H117" s="1" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A118" s="13" t="s">
-        <v>304</v>
-      </c>
-      <c r="B118" s="45" t="s">
-        <v>305</v>
-      </c>
-      <c r="C118" s="10"/>
-      <c r="D118" s="8">
-        <v>1</v>
-      </c>
-      <c r="E118" s="8">
-        <v>14.79</v>
-      </c>
-      <c r="F118" s="6">
-        <f t="shared" si="5"/>
-        <v>14.79</v>
-      </c>
-      <c r="H118" s="1" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A119" s="13"/>
-      <c r="B119" s="23"/>
-      <c r="C119" s="10"/>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A118" s="47"/>
+      <c r="B118" s="48"/>
+      <c r="C118" s="49"/>
+      <c r="D118" s="8"/>
+      <c r="E118" s="8"/>
+      <c r="F118" s="6"/>
+      <c r="H118" s="10"/>
+    </row>
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A119" s="47"/>
+      <c r="B119" s="48"/>
+      <c r="C119" s="49"/>
       <c r="D119" s="8"/>
       <c r="E119" s="8"/>
-      <c r="F119" s="6">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
+      <c r="F119" s="6"/>
       <c r="H119" s="10"/>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="13" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B120" s="23" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="C120" s="10" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D120" s="8">
         <v>2</v>
@@ -4673,77 +4666,57 @@
         <v>85.47</v>
       </c>
       <c r="F120" s="6">
-        <f t="shared" si="5"/>
+        <f>D120*E120</f>
         <v>170.94</v>
       </c>
       <c r="H120" s="46" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A121" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="B121" s="23" t="s">
-        <v>311</v>
-      </c>
-      <c r="C121" s="10" t="s">
-        <v>312</v>
-      </c>
-      <c r="D121" s="8">
-        <v>1</v>
-      </c>
-      <c r="E121" s="8">
-        <v>90.93</v>
-      </c>
-      <c r="F121" s="6">
-        <f t="shared" ref="F121:F127" si="6">D121*E121</f>
-        <v>90.93</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A122" s="13"/>
-      <c r="B122" s="23"/>
-      <c r="C122" s="10"/>
+        <v>302</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="39" t="s">
+        <v>298</v>
+      </c>
+      <c r="B121" s="40" t="s">
+        <v>288</v>
+      </c>
+      <c r="C121" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="D121" s="42">
+        <v>1</v>
+      </c>
+      <c r="E121" s="42">
+        <v>14.99</v>
+      </c>
+      <c r="F121" s="43">
+        <f>D121*E121</f>
+        <v>14.99</v>
+      </c>
+      <c r="G121" s="23"/>
+      <c r="H121" s="44" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A122" s="47"/>
+      <c r="B122" s="48"/>
+      <c r="C122" s="49"/>
       <c r="D122" s="8"/>
       <c r="E122" s="8"/>
-      <c r="F122" s="6">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
+      <c r="F122" s="6"/>
       <c r="H122" s="10"/>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A123" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="B123" s="23" t="s">
-        <v>316</v>
-      </c>
-      <c r="C123" s="10" t="s">
-        <v>317</v>
-      </c>
-      <c r="D123" s="8">
-        <v>1</v>
-      </c>
-      <c r="E123" s="8">
-        <v>93.8</v>
-      </c>
-      <c r="F123" s="6">
-        <f>D123*E123</f>
-        <v>93.8</v>
-      </c>
-      <c r="H123" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="I123" s="1" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A123" s="47"/>
+      <c r="B123" s="48"/>
+      <c r="C123" s="49"/>
+      <c r="D123" s="8"/>
+      <c r="E123" s="8"/>
+      <c r="F123" s="6"/>
+      <c r="H123" s="10"/>
+    </row>
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="13"/>
       <c r="B124" s="23"/>
       <c r="C124" s="10"/>
@@ -4755,38 +4728,38 @@
       </c>
       <c r="H124" s="10"/>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="13"/>
       <c r="B125" s="23"/>
       <c r="C125" s="10"/>
       <c r="D125" s="8"/>
       <c r="E125" s="8"/>
       <c r="F125" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="F121:F127" si="5">D125*E125</f>
         <v>0</v>
       </c>
       <c r="H125" s="10"/>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="13"/>
       <c r="B126" s="23"/>
       <c r="C126" s="10"/>
       <c r="D126" s="8"/>
       <c r="E126" s="8"/>
       <c r="F126" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H126" s="10"/>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="29"/>
       <c r="B127" s="23"/>
       <c r="C127" s="10"/>
       <c r="D127" s="30"/>
       <c r="E127" s="30"/>
       <c r="F127" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="H127" s="10"/>
@@ -4901,18 +4874,17 @@
     <hyperlink ref="H112" r:id="rId105" xr:uid="{9B1F77AB-62D5-44F5-A9D0-42268AD5ABAC}"/>
     <hyperlink ref="H113" r:id="rId106" display="https://www.grainger.com/product/Compression-Fitting-Coupling-20XM55" xr:uid="{EBAF2888-369A-453C-B808-5B36A12DBEF6}"/>
     <hyperlink ref="H114" r:id="rId107" xr:uid="{2F0D0D38-652B-44CC-BB9F-CAB0DB93A115}"/>
-    <hyperlink ref="H116" r:id="rId108" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C0D4D21-381D-4DE0-8627-C5CDD08AC966}"/>
-    <hyperlink ref="H117" r:id="rId109" display="https://www.grainger.com/product/Compression-Lug-3-8-in-Stud-24C366" xr:uid="{969E4A0C-E52F-4A17-A6F5-A3D01F24676B}"/>
-    <hyperlink ref="H118" r:id="rId110" display="https://www.digikey.com/en/products/detail/advantech-corporation/bb-mdr-40-48/7426468" xr:uid="{65E538F7-DA33-4388-B23E-404C55813446}"/>
-    <hyperlink ref="H120" r:id="rId111" display="https://www.grainger.com/product/Metal-Pipe-Flange-Flange-60WJ74" xr:uid="{851EBC08-2ED2-4124-B23F-E667A9F9321B}"/>
-    <hyperlink ref="H121" r:id="rId112" display="https://www.digikey.com/en/products/detail/pulse-egston/N1HLR-2700MV-KA-5V/29410171?gclid=d0e0296f6f231fb67a4543cf4f2a21d9&amp;gclsrc=3p.ds&amp;msclkid=d0e0296f6f231fb67a4543cf4f2a21d9" xr:uid="{54E9C926-24F1-4758-853F-BD129F6EBDFF}"/>
-    <hyperlink ref="I123" r:id="rId113" display="https://www.supplyhouse.com/Functional-Devices-TIB100A-Transformer-96VA-120-to-24-Vac-Circuit-Breaker-DIN-Rail-Mount?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{0A2C36B1-5125-4F51-8575-F092A696C03C}"/>
-    <hyperlink ref="H123" r:id="rId114" display="https://www.digikey.com/en/products/detail/aim-dynamics/TIB100A/28736836?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{74179639-4519-4C59-BD73-C785247C9073}"/>
+    <hyperlink ref="H121" r:id="rId108" display="https://www.grainger.com/product/20KF99?RIID=51819294775&amp;GID=729415832&amp;mid=OrderConfirmation_REST&amp;rfe=a98025ace82cfe3e9959eb0e2dd5f9501b4a446af591eb4540e15aea507809d7&amp;gucid=EMT:11126144:Item:CSM-323&amp;emcid=NA:Item" xr:uid="{2C0D4D21-381D-4DE0-8627-C5CDD08AC966}"/>
+    <hyperlink ref="H115" r:id="rId109" display="https://www.digikey.com/en/products/detail/advantech-corporation/bb-mdr-40-48/7426468" xr:uid="{65E538F7-DA33-4388-B23E-404C55813446}"/>
+    <hyperlink ref="H120" r:id="rId110" display="https://www.grainger.com/product/Metal-Pipe-Flange-Flange-60WJ74" xr:uid="{851EBC08-2ED2-4124-B23F-E667A9F9321B}"/>
+    <hyperlink ref="H117" r:id="rId111" display="https://www.digikey.com/en/products/detail/pulse-egston/N1HLR-2700MV-KA-5V/29410171?gclid=d0e0296f6f231fb67a4543cf4f2a21d9&amp;gclsrc=3p.ds&amp;msclkid=d0e0296f6f231fb67a4543cf4f2a21d9" xr:uid="{54E9C926-24F1-4758-853F-BD129F6EBDFF}"/>
+    <hyperlink ref="I116" r:id="rId112" display="https://www.supplyhouse.com/Functional-Devices-TIB100A-Transformer-96VA-120-to-24-Vac-Circuit-Breaker-DIN-Rail-Mount?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{0A2C36B1-5125-4F51-8575-F092A696C03C}"/>
+    <hyperlink ref="H116" r:id="rId113" display="https://www.digikey.com/en/products/detail/aim-dynamics/TIB100A/28736836?msockid=277021126b6a6b6a3cca367a6a576a6d" xr:uid="{74179639-4519-4C59-BD73-C785247C9073}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId115"/>
+  <pageSetup orientation="portrait" r:id="rId114"/>
   <tableParts count="1">
-    <tablePart r:id="rId116"/>
+    <tablePart r:id="rId115"/>
   </tableParts>
 </worksheet>
 </file>